--- a/public/templates/projects_template.xlsx
+++ b/public/templates/projects_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:K7"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -410,7 +410,6 @@
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,9 +444,6 @@
         <v>已签署合同</v>
       </c>
       <c r="K1" t="str">
-        <v>结算段数</v>
-      </c>
-      <c r="L1" t="str">
         <v>归属年份</v>
       </c>
     </row>
@@ -483,9 +479,6 @@
         <v>TRUE</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
         <v>2026</v>
       </c>
     </row>
@@ -521,9 +514,6 @@
         <v>TRUE</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
         <v>2026</v>
       </c>
     </row>
@@ -559,9 +549,6 @@
         <v>TRUE</v>
       </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
         <v>2026</v>
       </c>
     </row>
@@ -597,9 +584,6 @@
         <v>FALSE</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
         <v>2026</v>
       </c>
     </row>
@@ -635,9 +619,6 @@
         <v>FALSE</v>
       </c>
       <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
         <v>2026</v>
       </c>
     </row>
@@ -673,15 +654,12 @@
         <v>TRUE</v>
       </c>
       <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
         <v>2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/projects_template.xlsx
+++ b/public/templates/projects_template.xlsx
@@ -1,46 +1,190 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guanjianfei/sales-project-manager/public/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49B1ADA-C9D2-A748-9DAD-0B49D3C1CE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="项目导入模板" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+  <si>
+    <t>项目名称*</t>
+  </si>
+  <si>
+    <t>客户名称*</t>
+  </si>
+  <si>
+    <t>项目描述</t>
+  </si>
+  <si>
+    <t>项目状态</t>
+  </si>
+  <si>
+    <t>项目金额</t>
+  </si>
+  <si>
+    <t>成功概率</t>
+  </si>
+  <si>
+    <t>开始日期</t>
+  </si>
+  <si>
+    <t>预期关闭日期</t>
+  </si>
+  <si>
+    <t>有开工函</t>
+  </si>
+  <si>
+    <t>已签署合同</t>
+  </si>
+  <si>
+    <t>归属年份</t>
+  </si>
+  <si>
+    <t>企业官网开发</t>
+  </si>
+  <si>
+    <t>陈明</t>
+  </si>
+  <si>
+    <t>为客户开发响应式企业官网，包含PC端和移动端</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>ERP系统实施</t>
+  </si>
+  <si>
+    <t>李华</t>
+  </si>
+  <si>
+    <t>ERP系统的部署、配置和员工培训</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>移动应用开发</t>
+  </si>
+  <si>
+    <t>王芳</t>
+  </si>
+  <si>
+    <t>开发iOS和Android双平台移动应用</t>
+  </si>
+  <si>
+    <t>won</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>数据分析平台</t>
+  </si>
+  <si>
+    <t>赵强</t>
+  </si>
+  <si>
+    <t>大数据分析与可视化平台开发</t>
+  </si>
+  <si>
+    <t>lost</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>年度运维服务</t>
+  </si>
+  <si>
+    <t>刘伟</t>
+  </si>
+  <si>
+    <t>IT基础设施运维和技术支持服务</t>
+  </si>
+  <si>
+    <t>on_hold</t>
+  </si>
+  <si>
+    <t>电商平台建设</t>
+  </si>
+  <si>
+    <t>孙丽</t>
+  </si>
+  <si>
+    <t>B2C电商平台开发，包含支付和物流集成</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
+  </si>
+  <si>
+    <t>成交日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -64,14 +208,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,69 +549,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="4" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="7" max="8" width="15.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>项目名称*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>客户名称*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>项目描述</v>
-      </c>
-      <c r="D1" t="str">
-        <v>项目状态</v>
-      </c>
-      <c r="E1" t="str">
-        <v>项目金额</v>
-      </c>
-      <c r="F1" t="str">
-        <v>成功概率</v>
-      </c>
-      <c r="G1" t="str">
-        <v>开始日期</v>
-      </c>
-      <c r="H1" t="str">
-        <v>预期关闭日期</v>
-      </c>
-      <c r="I1" t="str">
-        <v>有开工函</v>
-      </c>
-      <c r="J1" t="str">
-        <v>已签署合同</v>
-      </c>
-      <c r="K1" t="str">
-        <v>归属年份</v>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>企业官网开发</v>
-      </c>
-      <c r="B2" t="str">
-        <v>陈明</v>
-      </c>
-      <c r="C2" t="str">
-        <v>为客户开发响应式企业官网，包含PC端和移动端</v>
-      </c>
-      <c r="D2" t="str">
-        <v>active</v>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
       </c>
       <c r="E2">
         <v>50000</v>
@@ -466,34 +621,34 @@
       <c r="F2">
         <v>75</v>
       </c>
-      <c r="G2" t="str">
-        <v>2026-01-15</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-06-30</v>
-      </c>
-      <c r="I2" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J2" t="str">
-        <v>TRUE</v>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
       </c>
       <c r="K2">
         <v>2026</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ERP系统实施</v>
-      </c>
-      <c r="B3" t="str">
-        <v>李华</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ERP系统的部署、配置和员工培训</v>
-      </c>
-      <c r="D3" t="str">
-        <v>active</v>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
       <c r="E3">
         <v>120000</v>
@@ -501,34 +656,34 @@
       <c r="F3">
         <v>60</v>
       </c>
-      <c r="G3" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-12-31</v>
-      </c>
-      <c r="I3" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J3" t="str">
-        <v>TRUE</v>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
       </c>
       <c r="K3">
         <v>2026</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>移动应用开发</v>
-      </c>
-      <c r="B4" t="str">
-        <v>王芳</v>
-      </c>
-      <c r="C4" t="str">
-        <v>开发iOS和Android双平台移动应用</v>
-      </c>
-      <c r="D4" t="str">
-        <v>won</v>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
       </c>
       <c r="E4">
         <v>80000</v>
@@ -536,69 +691,72 @@
       <c r="F4">
         <v>100</v>
       </c>
-      <c r="G4" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J4" t="str">
-        <v>TRUE</v>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
       </c>
       <c r="K4">
         <v>2026</v>
       </c>
+      <c r="L4" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>数据分析平台</v>
-      </c>
-      <c r="B5" t="str">
-        <v>赵强</v>
-      </c>
-      <c r="C5" t="str">
-        <v>大数据分析与可视化平台开发</v>
-      </c>
-      <c r="D5" t="str">
-        <v>lost</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="H5" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="I5" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J5" t="str">
-        <v>FALSE</v>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
       </c>
       <c r="K5">
         <v>2026</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>年度运维服务</v>
-      </c>
-      <c r="B6" t="str">
-        <v>刘伟</v>
-      </c>
-      <c r="C6" t="str">
-        <v>IT基础设施运维和技术支持服务</v>
-      </c>
-      <c r="D6" t="str">
-        <v>on_hold</v>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
       </c>
       <c r="E6">
         <v>30000</v>
@@ -606,34 +764,34 @@
       <c r="F6">
         <v>50</v>
       </c>
-      <c r="G6" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="H6" t="str">
-        <v>2026-12-31</v>
-      </c>
-      <c r="I6" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J6" t="str">
-        <v>FALSE</v>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
       </c>
       <c r="K6">
         <v>2026</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>电商平台建设</v>
-      </c>
-      <c r="B7" t="str">
-        <v>孙丽</v>
-      </c>
-      <c r="C7" t="str">
-        <v>B2C电商平台开发，包含支付和物流集成</v>
-      </c>
-      <c r="D7" t="str">
-        <v>active</v>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -641,25 +799,27 @@
       <c r="F7">
         <v>80</v>
       </c>
-      <c r="G7" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="H7" t="str">
-        <v>2027-03-31</v>
-      </c>
-      <c r="I7" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J7" t="str">
-        <v>TRUE</v>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
       </c>
       <c r="K7">
         <v>2026</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError sqref="A1:K7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>